--- a/InputData/trans/BVTStL/Boolean Veh Types Subject to LCFS.xlsx
+++ b/InputData/trans/BVTStL/Boolean Veh Types Subject to LCFS.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Documents\eps-us\InputData\trans\BVTStL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\trans\BVTStL\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B748A387-264B-4ED0-9400-910230BD852C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="23955" windowHeight="11325"/>
+    <workbookView xWindow="735" yWindow="720" windowWidth="26730" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -76,19 +77,19 @@
     <t>Page 15</t>
   </si>
   <si>
-    <t>BVTStL Boolean Vehicle Types Subject to LCFS</t>
-  </si>
-  <si>
     <t>(Boolean)</t>
   </si>
   <si>
     <t>Based on the California LCFS, we choose to exempt aircraft.</t>
+  </si>
+  <si>
+    <t>BVTStL BAU Vehicle Types Subject to LCFS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -153,9 +154,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -193,9 +194,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -230,7 +231,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -265,7 +266,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -438,16 +439,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -455,54 +456,54 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>2015</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -512,21 +513,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.1328125" customWidth="1"/>
-    <col min="2" max="2" width="15.1328125" customWidth="1"/>
-    <col min="3" max="3" width="13.1328125" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>8</v>
@@ -535,7 +536,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -546,7 +547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -557,7 +558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -568,7 +569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -579,7 +580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -590,7 +591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
